--- a/reports/templates/opt_1a_single.xlsx
+++ b/reports/templates/opt_1a_single.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nmsceduph-my.sharepoint.com/personal/johnryan_magusara_nmsc_edu_ph/Documents/USTP/Capstone Project 2026/Generate Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\nutriwatch_api\reports\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{A97EF2F7-B7A6-4E61-9DC1-F4D8C7138F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2B78F0F-1342-4AC6-B598-57398F866FEC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E623CC1B-5A83-4913-8666-287BED510BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1EF09E0D-DA90-4B2C-8B4C-BD0F3485DC17}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t/>
   </si>
@@ -222,20 +222,14 @@
   <si>
     <t>NONE, +1, +2, +3</t>
   </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\ dd\,\ yyyy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-dd\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]mmm\-dd\-yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="mm/dd/yyyy;@"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -398,7 +392,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -586,73 +580,8 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,7 +590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -747,6 +676,168 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -759,15 +850,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -775,197 +866,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -974,7 +875,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill>
@@ -990,38 +891,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <fgColor theme="0"/>
@@ -1031,109 +900,8 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightHorizontal"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightHorizontal"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill patternType="solid"/>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1159,16 +927,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1202,103 +960,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFCC"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFCC"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1334,21 +1000,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1360,10 +1011,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1683,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D0191D-690B-4FC4-827D-F182ED993577}">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -1698,10 +1345,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1710,49 +1357,49 @@
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74" t="s">
+      <c r="F1" s="26"/>
+      <c r="G1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="75" t="s">
+      <c r="H1" s="27"/>
+      <c r="I1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="76" t="s">
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="77"/>
-      <c r="N1" s="59" t="s">
+      <c r="M1" s="40"/>
+      <c r="N1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="61"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="31"/>
     </row>
     <row r="2" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="72"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="25"/>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63">
+      <c r="F2" s="32"/>
+      <c r="G2" s="33">
         <v>0</v>
       </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="64" t="s">
+      <c r="H2" s="33"/>
+      <c r="I2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="65"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="35"/>
       <c r="N2" s="5"/>
       <c r="O2" s="6"/>
       <c r="P2" s="7"/>
@@ -1760,80 +1407,80 @@
     <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
       <c r="K3" s="10"/>
-      <c r="L3" s="68" t="s">
+      <c r="L3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
       <c r="P3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44" t="s">
+      <c r="I4" s="46"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="48" t="s">
+      <c r="L4" s="49"/>
+      <c r="M4" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
       <c r="P4" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="15"/>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="55" t="s">
+      <c r="I5" s="57"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="56"/>
-      <c r="O5" s="57">
+      <c r="N5" s="60"/>
+      <c r="O5" s="61">
         <v>46100</v>
       </c>
-      <c r="P5" s="58"/>
+      <c r="P5" s="62"/>
     </row>
-    <row r="6" spans="1:16" ht="54" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>13</v>
       </c>
@@ -1879,109 +1526,60 @@
       <c r="O6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="41" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="O7" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="37"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
+      <c r="P7" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="H4:J4"/>
@@ -1991,150 +1589,59 @@
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:P8">
-    <cfRule type="expression" dxfId="37" priority="5">
-      <formula>$N$2=""</formula>
-    </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="36" priority="12">
-      <formula>LEN(TRIM(A8))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>AND($A$1&lt;&gt;"",$B$1="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>$A$1=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="expression" dxfId="33" priority="11">
-      <formula>AND(A8&lt;&gt;"", B8=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="32" priority="37" stopIfTrue="1"/>
-    <cfRule type="containsBlanks" dxfId="31" priority="36">
-      <formula>LEN(TRIM(C8))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="35">
-      <formula>AND(A8&lt;&gt;"", C8="")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C3:G3">
-    <cfRule type="containsText" dxfId="29" priority="18" operator="containsText" text="found">
+    <cfRule type="containsText" dxfId="8" priority="18" operator="containsText" text="found">
       <formula>NOT(ISERROR(SEARCH("found",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="containsBlanks" dxfId="28" priority="32">
-      <formula>LEN(TRIM(D8))=0</formula>
-    </cfRule>
-    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
-    <cfRule type="expression" dxfId="26" priority="30">
-      <formula>AND(A8&lt;&gt;"", D8=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="25" priority="10">
-      <formula>AND(A8&lt;&gt;"", E8="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="24" priority="9">
-      <formula>AND(A8&lt;&gt;"", F8="")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="29" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="expression" dxfId="21" priority="8">
-      <formula>AND(A8&lt;&gt;"", G8="")</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="6" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:H2">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3 L3">
-    <cfRule type="containsText" dxfId="19" priority="33" operator="containsText" text="repeated">
+    <cfRule type="containsText" dxfId="4" priority="33" operator="containsText" text="repeated">
       <formula>NOT(ISERROR(SEARCH("repeated",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="expression" dxfId="18" priority="23">
-      <formula>IF(P8&gt;59,P8&lt;1500)</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="24" operator="between">
-      <formula>0.001</formula>
-      <formula>2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="25" operator="between">
-      <formula>32.001</formula>
-      <formula>5000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="26" operator="between">
-      <formula>28.001</formula>
-      <formula>32</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="27">
-      <formula>IF(K8&gt;59,K8&lt;5000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="22">
-      <formula>$A$8&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="17">
-      <formula>J8&lt;I8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8:J8">
-    <cfRule type="containsBlanks" dxfId="11" priority="14">
-      <formula>LEN(TRIM(I8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>AND(N2&lt;&gt;"",O2&lt;&gt;"",P2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
-    <cfRule type="expression" dxfId="9" priority="21">
-      <formula>IF(K8&gt;59,K8&lt;5000)</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="between">
-      <formula>126.001</formula>
-      <formula>5000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="20" operator="between">
-      <formula>0.001</formula>
-      <formula>43.5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K3 P3">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="28">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="28">
       <formula>LEN(TRIM(K3))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="15" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="31">
-      <formula>AND(D8&lt;&gt;"",K8&gt;23)</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="No Birthdate">
-      <formula>NOT(ISERROR(SEARCH("No Birthdate",K8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
@@ -2150,13 +1657,13 @@
   <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="IMPORTANT:" prompt="Pls indicate the date for the next round of OPT Plus measurements. This will ensure calculation of children's age in months for this form." sqref="N1:P1" xr:uid="{11D02138-D5F9-42EE-8C94-9B57FBDB58DF}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose year" sqref="P2" xr:uid="{8DCBE5E4-EEF1-4142-A4BF-B8AA5D6535EE}">
-      <formula1>$AA$3:$AA$15</formula1>
+      <formula1>$AA$3:$AA$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose date" sqref="O2" xr:uid="{80E94D11-8609-47F9-8743-B96D9F783C66}">
-      <formula1>$Z$3:$Z$33</formula1>
+      <formula1>$Z$3:$Z$32</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose month" sqref="N2" xr:uid="{AD1B94E7-0FB2-464F-AC42-A515E08AE83E}">
-      <formula1>$Y$3:$Y$14</formula1>
+      <formula1>$Y$3:$Y$13</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
